--- a/NBFC-MF/Borrowers/Wangkheimayum_Guni_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Wangkheimayum_Guni_Weekly.xlsx
@@ -827,31 +827,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>540.8517343859711</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>1559.1482656140288</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>25413.899133040686</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>4586.1008669593139</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -1120,7 +1122,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1155,7 +1157,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>31500</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1190,7 +1192,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>26973.047398654715</v>
+        <v>25413.899133040686</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3026.9526013452851</v>
+        <v>4586.1008669593139</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Wangkheimayum_Guni_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Wangkheimayum_Guni_Weekly.xlsx
@@ -861,31 +861,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
+      <c r="A5" s="19">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>509.58837614695045</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>1590.4116238530496</v>
+      </c>
+      <c r="G5" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>23823.487509187638</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>6176.5124908123616</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -1122,7 +1124,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1157,7 +1159,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>29400</v>
+        <v>27300</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1192,7 +1194,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>25413.899133040686</v>
+        <v>23823.487509187638</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1227,7 +1229,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4586.1008669593139</v>
+        <v>6176.5124908123616</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Wangkheimayum_Guni_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Wangkheimayum_Guni_Weekly.xlsx
@@ -895,31 +895,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
+      <c r="A6" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B6" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>477.69813873938818</v>
+      </c>
+      <c r="F6" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
+        <v>1622.3018612606118</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>22201.185647927028</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>7798.8143520729718</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -927,31 +929,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46302</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>445.16845225671983</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>1654.8315477432802</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>20546.354100183748</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>9453.6458998162525</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1124,7 +1128,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>27300</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1194,7 +1198,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>23823.487509187638</v>
+        <v>20546.354100183748</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1229,7 +1233,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6176.5124908123616</v>
+        <v>9453.6458998162525</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
